--- a/data/trans_dic/P1408-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1408-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,04</t>
+          <t>2,26; 5,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,26</t>
+          <t>2,13; 5,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,56</t>
+          <t>0,72; 2,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,76</t>
+          <t>2,19; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,45</t>
+          <t>1,15; 3,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,15</t>
+          <t>0,92; 3,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,59</t>
+          <t>0,64; 2,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,84</t>
+          <t>1,91; 3,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,71</t>
+          <t>2,01; 3,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,8</t>
+          <t>1,77; 3,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,2</t>
+          <t>0,9; 2,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,81</t>
+          <t>2,25; 3,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,63</t>
+          <t>3,7; 6,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,04</t>
+          <t>1,19; 3,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,24</t>
+          <t>1,36; 3,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,88</t>
+          <t>1,59; 3,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,8</t>
+          <t>1,69; 3,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,75</t>
+          <t>0,5; 1,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,4</t>
+          <t>0,75; 2,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,98</t>
+          <t>1,79; 3,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,9</t>
+          <t>3,07; 4,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,03</t>
+          <t>0,97; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,43</t>
+          <t>1,21; 2,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,91</t>
+          <t>1,87; 3,27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,25</t>
+          <t>2,26; 5,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,41</t>
+          <t>1,07; 3,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,84</t>
+          <t>0,85; 2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,66</t>
+          <t>1,43; 3,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,45</t>
+          <t>2,05; 4,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,82</t>
+          <t>0,41; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,13</t>
+          <t>0,92; 2,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,57</t>
+          <t>1,19; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,34</t>
+          <t>2,5; 4,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,17</t>
+          <t>0,89; 2,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,55</t>
+          <t>1,09; 2,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,72</t>
+          <t>1,5; 2,84</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,38</t>
+          <t>3,07; 5,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,5</t>
+          <t>0,96; 2,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,55</t>
+          <t>1,6; 3,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,39</t>
+          <t>1,85; 3,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,18</t>
+          <t>1,95; 4,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,02</t>
+          <t>0,76; 2,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,5</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,91</t>
+          <t>2,22; 4,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,4</t>
+          <t>2,76; 4,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,0</t>
+          <t>0,96; 2,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,14</t>
+          <t>1,05; 2,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,42</t>
+          <t>2,27; 3,52</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,82</t>
+          <t>3,54; 4,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,73</t>
+          <t>1,61; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,46</t>
+          <t>1,53; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,94</t>
+          <t>2,05; 3,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,33</t>
+          <t>2,2; 3,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,65</t>
+          <t>0,87; 1,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,71</t>
+          <t>0,88; 1,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,97</t>
+          <t>2,17; 3,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,9</t>
+          <t>3,0; 3,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,99</t>
+          <t>1,37; 2,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,33; 1,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,84</t>
+          <t>2,2; 2,92</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>41658</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14938; 34993</t>
+          <t>15663; 34681</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14894; 37037</t>
+          <t>14949; 38325</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5014; 17261</t>
+          <t>4837; 17303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14328; 30277</t>
+          <t>15123; 32385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7913; 23735</t>
+          <t>7942; 22722</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6143; 21989</t>
+          <t>6440; 21225</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4337; 17456</t>
+          <t>4274; 16934</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13764; 25887</t>
+          <t>13981; 26756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26231; 51241</t>
+          <t>27729; 51455</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26487; 53176</t>
+          <t>24837; 50541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11561; 29679</t>
+          <t>12140; 29233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29694; 49912</t>
+          <t>32055; 52926</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>27160</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>51402</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36108; 63780</t>
+          <t>35588; 65243</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12102; 30944</t>
+          <t>12130; 30595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13752; 33089</t>
+          <t>13955; 33016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11854; 34356</t>
+          <t>16667; 34406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15958; 36822</t>
+          <t>16321; 38564</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5174; 17970</t>
+          <t>5107; 17668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8377; 25058</t>
+          <t>7833; 24599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17711; 38082</t>
+          <t>19095; 41255</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59550; 94576</t>
+          <t>59171; 92607</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19593; 41569</t>
+          <t>19822; 42172</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25291; 50245</t>
+          <t>24920; 50193</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30903; 62478</t>
+          <t>39682; 69376</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30713</t>
+          <t>33348</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15368; 35613</t>
+          <t>15318; 34718</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8182; 25848</t>
+          <t>8095; 25214</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6477; 21602</t>
+          <t>6474; 22157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10530; 25750</t>
+          <t>11428; 28835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13236; 30421</t>
+          <t>14042; 32382</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3140; 14117</t>
+          <t>3180; 14895</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7450; 24591</t>
+          <t>7227; 23225</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5627; 23955</t>
+          <t>9615; 24616</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33456; 59138</t>
+          <t>34066; 59612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13599; 33247</t>
+          <t>13586; 32863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17358; 39332</t>
+          <t>16818; 38453</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19309; 44378</t>
+          <t>24159; 45806</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>59408</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27401; 50656</t>
+          <t>28888; 52027</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8187; 23669</t>
+          <t>9076; 25320</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14875; 33311</t>
+          <t>14957; 33269</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16068; 31402</t>
+          <t>18291; 36428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21530; 43464</t>
+          <t>20263; 41846</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7532; 21281</t>
+          <t>8009; 22228</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3336; 15697</t>
+          <t>3281; 15026</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21913; 42680</t>
+          <t>24832; 45051</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54662; 87086</t>
+          <t>54633; 86818</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19109; 40079</t>
+          <t>19130; 40160</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20983; 42343</t>
+          <t>20870; 43701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42421; 68971</t>
+          <t>47849; 74186</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>113437; 157978</t>
+          <t>116127; 161980</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56944; 93437</t>
+          <t>55218; 91308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51201; 83469</t>
+          <t>51915; 84355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62876; 101720</t>
+          <t>72487; 107672</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>73793; 112672</t>
+          <t>74356; 110814</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31756; 58506</t>
+          <t>30856; 57667</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33464; 60705</t>
+          <t>31237; 60482</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>70208; 108383</t>
+          <t>81023; 113973</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>198466; 259841</t>
+          <t>199435; 257911</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95569; 139176</t>
+          <t>95606; 141689</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91677; 132478</t>
+          <t>92622; 132714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>144396; 201656</t>
+          <t>159961; 211854</t>
         </is>
       </c>
     </row>
